--- a/threagile/output/stride/risks.xlsx
+++ b/threagile/output/stride/risks.xlsx
@@ -10,73 +10,73 @@
     <sheet name="VaultNote Threat Model" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'VaultNote Threat Model'!$A$1:$T$36</definedName>
+    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'VaultNote Threat Model'!$A$1:$T$37</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="228">
+  <si>
+    <t>Identified Risk</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>STRIDE</t>
+  </si>
+  <si>
+    <t>Function</t>
+  </si>
+  <si>
+    <t>CWE</t>
+  </si>
+  <si>
+    <t>Risk Category</t>
+  </si>
+  <si>
+    <t>Communication Link</t>
+  </si>
+  <si>
+    <t>RAA %</t>
+  </si>
+  <si>
+    <t>Ticket</t>
+  </si>
+  <si>
+    <t>Severity</t>
+  </si>
+  <si>
+    <t>Likelihood</t>
+  </si>
+  <si>
+    <t>Impact</t>
+  </si>
+  <si>
+    <t>Technical Asset</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Mitigation</t>
+  </si>
+  <si>
+    <t>Check</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Justification</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
   <si>
     <t>Checked by</t>
-  </si>
-  <si>
-    <t>Ticket</t>
-  </si>
-  <si>
-    <t>STRIDE</t>
-  </si>
-  <si>
-    <t>Function</t>
-  </si>
-  <si>
-    <t>Risk Category</t>
-  </si>
-  <si>
-    <t>Check</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Severity</t>
-  </si>
-  <si>
-    <t>Likelihood</t>
-  </si>
-  <si>
-    <t>Impact</t>
-  </si>
-  <si>
-    <t>CWE</t>
-  </si>
-  <si>
-    <t>Justification</t>
-  </si>
-  <si>
-    <t>Technical Asset</t>
-  </si>
-  <si>
-    <t>RAA %</t>
-  </si>
-  <si>
-    <t>Action</t>
-  </si>
-  <si>
-    <t>Mitigation</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Communication Link</t>
-  </si>
-  <si>
-    <t>Identified Risk</t>
   </si>
   <si>
     <t>High</t>
@@ -180,12 +180,42 @@
     <t>Likely</t>
   </si>
   <si>
+    <t>Lateral Movement</t>
+  </si>
+  <si>
+    <t>Architecture</t>
+  </si>
+  <si>
+    <t>CWE-0</t>
+  </si>
+  <si>
+    <t>Lateral Movement via Shared Runtime</t>
+  </si>
+  <si>
+    <t>Nginx Reverse Proxy</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Lateral Movement via Shared Runtime on Docker Host: assets from 3 trust zones co-located</t>
+  </si>
+  <si>
+    <t>Runtime Isolation</t>
+  </si>
+  <si>
+    <t>Separate assets from different trust zones onto dedicated runtimes (separate node pools, dedicated VMs, distinct container namespaces with NetworkPolicy). Apply seccomp/AppArmor profiles and disable privilege escalation.</t>
+  </si>
+  <si>
+    <t>Are high-trust and low-trust assets co-located on the same shared runtime?</t>
+  </si>
+  <si>
+    <t>lateral-movement-shared-runtime@docker-host</t>
+  </si>
+  <si>
     <t>Elevation of Privilege</t>
   </si>
   <si>
-    <t>Architecture</t>
-  </si>
-  <si>
     <t>CWE-306</t>
   </si>
   <si>
@@ -238,12 +268,6 @@
   </si>
   <si>
     <t>Missing Content-Security-Policy Header on Web Entry Point</t>
-  </si>
-  <si>
-    <t>Nginx Reverse Proxy</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>Missing Content-Security-Policy: Nginx Reverse Proxy serves browser clients handling auth tokens without a verified CSP header</t>
@@ -1234,13 +1258,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D1" s="24" t="s">
         <v>2</v>
@@ -1249,49 +1273,49 @@
         <v>3</v>
       </c>
       <c r="F1" s="24" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G1" s="24" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1" s="24" t="s">
         <v>12</v>
       </c>
       <c r="I1" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="L1" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="O1" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="P1" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="R1" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="K1" s="24" t="s">
+      <c r="S1" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="M1" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="N1" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="O1" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="P1" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q1" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="R1" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="24" t="s">
-        <v>0</v>
-      </c>
       <c r="T1" s="24" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2">
@@ -1503,28 +1527,28 @@
         <v>56</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="J5" s="18" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L5" s="23" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M5" s="23" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N5" s="23" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="O5" s="20" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P5" s="10" t="s">
         <v>34</v>
@@ -1547,46 +1571,46 @@
         <v>47</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="J6" s="18" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="K6" s="19" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L6" s="23" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M6" s="23" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N6" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O6" s="20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P6" s="10" t="s">
         <v>34</v>
@@ -1609,46 +1633,46 @@
         <v>47</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>23</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J7" s="18" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K7" s="19" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L7" s="23" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M7" s="23" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N7" s="23" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="O7" s="20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P7" s="10" t="s">
         <v>34</v>
@@ -1677,40 +1701,40 @@
         <v>48</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>23</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J8" s="18" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="K8" s="19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L8" s="23" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M8" s="23" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N8" s="23" t="s">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="O8" s="20" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="P8" s="10" t="s">
         <v>34</v>
@@ -1745,34 +1769,34 @@
         <v>23</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>86</v>
+        <v>39</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J9" s="18" t="s">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="K9" s="19" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L9" s="23" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="M9" s="23" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="N9" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O9" s="20" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="P9" s="10" t="s">
         <v>34</v>
@@ -1791,50 +1815,50 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="H10" s="7" t="s">
+      <c r="F10" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J10" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="K10" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="L10" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="I10" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="J10" s="18" t="s">
+      <c r="M10" s="23" t="s">
         <v>92</v>
-      </c>
-      <c r="K10" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="L10" s="23" t="s">
-        <v>83</v>
-      </c>
-      <c r="M10" s="23" t="s">
-        <v>84</v>
       </c>
       <c r="N10" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O10" s="20" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="P10" s="10" t="s">
         <v>34</v>
@@ -1853,50 +1877,50 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="6" t="s">
+      <c r="A11" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>97</v>
+      <c r="B11" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>27</v>
       </c>
       <c r="J11" s="18" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="K11" s="19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L11" s="23" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="M11" s="23" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="N11" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O11" s="20" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P11" s="10" t="s">
         <v>34</v>
@@ -1919,7 +1943,7 @@
         <v>47</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>48</v>
@@ -1931,34 +1955,34 @@
         <v>36</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>39</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="J12" s="18" t="s">
         <v>41</v>
       </c>
       <c r="K12" s="19" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="L12" s="23" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="M12" s="23" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="N12" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O12" s="20" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="P12" s="10" t="s">
         <v>34</v>
@@ -1984,43 +2008,43 @@
         <v>52</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>39</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="J13" s="18" t="s">
         <v>41</v>
       </c>
       <c r="K13" s="19" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="L13" s="23" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M13" s="23" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="N13" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O13" s="20" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P13" s="10" t="s">
         <v>34</v>
@@ -2055,34 +2079,34 @@
         <v>23</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>39</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="J14" s="18" t="s">
         <v>41</v>
       </c>
       <c r="K14" s="19" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="L14" s="23" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="M14" s="23" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="N14" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O14" s="20" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="P14" s="10" t="s">
         <v>34</v>
@@ -2117,34 +2141,34 @@
         <v>23</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>39</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="J15" s="18" t="s">
         <v>41</v>
       </c>
       <c r="K15" s="19" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="L15" s="23" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="M15" s="23" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="N15" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O15" s="20" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="P15" s="10" t="s">
         <v>34</v>
@@ -2170,7 +2194,7 @@
         <v>52</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>22</v>
@@ -2179,49 +2203,49 @@
         <v>23</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="J16" s="18" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="K16" s="19" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="L16" s="23" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="M16" s="23" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="N16" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O16" s="20" t="s">
-        <v>119</v>
-      </c>
-      <c r="P16" s="12" t="s">
-        <v>120</v>
+        <v>125</v>
+      </c>
+      <c r="P16" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="Q16" s="19" t="s">
-        <v>121</v>
+        <v>27</v>
       </c>
       <c r="R16" s="17" t="s">
-        <v>122</v>
+        <v>27</v>
       </c>
       <c r="S16" s="17" t="s">
-        <v>123</v>
+        <v>27</v>
       </c>
       <c r="T16" s="16" t="s">
-        <v>124</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17">
@@ -2235,55 +2259,55 @@
         <v>48</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="G17" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J17" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="K17" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="H17" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J17" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="K17" s="19" t="s">
-        <v>127</v>
-      </c>
       <c r="L17" s="23" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="M17" s="23" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="N17" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O17" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="P17" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q17" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="R17" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="P17" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q17" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="R17" s="17" t="s">
-        <v>27</v>
-      </c>
       <c r="S17" s="17" t="s">
-        <v>27</v>
+        <v>131</v>
       </c>
       <c r="T17" s="16" t="s">
-        <v>27</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18">
@@ -2297,40 +2321,40 @@
         <v>48</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>54</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="J18" s="18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K18" s="19" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="L18" s="23" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="M18" s="23" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="N18" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O18" s="20" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="P18" s="10" t="s">
         <v>34</v>
@@ -2349,50 +2373,50 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E19" s="8" t="s">
+      <c r="D19" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="F19" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>97</v>
+      <c r="F19" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="J19" s="18" t="s">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="K19" s="19" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="L19" s="23" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="M19" s="23" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="N19" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O19" s="20" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="P19" s="10" t="s">
         <v>34</v>
@@ -2415,46 +2439,46 @@
         <v>48</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G20" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="J20" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K20" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="L20" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="H20" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="J20" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="K20" s="19" t="s">
+      <c r="M20" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="L20" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="M20" s="23" t="s">
-        <v>139</v>
-      </c>
       <c r="N20" s="23" t="s">
-        <v>140</v>
+        <v>45</v>
       </c>
       <c r="O20" s="20" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P20" s="10" t="s">
         <v>34</v>
@@ -2477,7 +2501,7 @@
         <v>48</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>20</v>
@@ -2489,34 +2513,34 @@
         <v>23</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="I21" s="7" t="s">
         <v>27</v>
       </c>
       <c r="J21" s="18" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="K21" s="19" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="L21" s="23" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="M21" s="23" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="N21" s="23" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="O21" s="20" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="P21" s="10" t="s">
         <v>34</v>
@@ -2539,7 +2563,7 @@
         <v>48</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>20</v>
@@ -2551,34 +2575,34 @@
         <v>23</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="I22" s="7" t="s">
         <v>27</v>
       </c>
       <c r="J22" s="18" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="K22" s="19" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="L22" s="23" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="M22" s="23" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="N22" s="23" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="O22" s="20" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="P22" s="10" t="s">
         <v>34</v>
@@ -2601,10 +2625,10 @@
         <v>48</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>35</v>
@@ -2613,34 +2637,34 @@
         <v>23</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="I23" s="7" t="s">
         <v>27</v>
       </c>
       <c r="J23" s="18" t="s">
-        <v>28</v>
+        <v>95</v>
       </c>
       <c r="K23" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="L23" s="23" t="s">
         <v>146</v>
       </c>
-      <c r="L23" s="23" t="s">
-        <v>138</v>
-      </c>
       <c r="M23" s="23" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="N23" s="23" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="O23" s="20" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="P23" s="10" t="s">
         <v>34</v>
@@ -2663,7 +2687,7 @@
         <v>48</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>48</v>
@@ -2675,34 +2699,34 @@
         <v>23</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>91</v>
+        <v>26</v>
       </c>
       <c r="I24" s="7" t="s">
         <v>27</v>
       </c>
       <c r="J24" s="18" t="s">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="K24" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="L24" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="M24" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="N24" s="23" t="s">
         <v>148</v>
       </c>
-      <c r="L24" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="M24" s="23" t="s">
-        <v>139</v>
-      </c>
-      <c r="N24" s="23" t="s">
-        <v>140</v>
-      </c>
       <c r="O24" s="20" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="P24" s="10" t="s">
         <v>34</v>
@@ -2725,7 +2749,7 @@
         <v>48</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>48</v>
@@ -2734,37 +2758,37 @@
         <v>35</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="I25" s="7" t="s">
         <v>27</v>
       </c>
       <c r="J25" s="18" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="K25" s="19" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="L25" s="23" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="M25" s="23" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="N25" s="23" t="s">
-        <v>45</v>
+        <v>148</v>
       </c>
       <c r="O25" s="20" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="P25" s="10" t="s">
         <v>34</v>
@@ -2787,46 +2811,46 @@
         <v>48</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>48</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>156</v>
+        <v>35</v>
       </c>
       <c r="E26" s="8" t="s">
         <v>54</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="I26" s="7" t="s">
         <v>27</v>
       </c>
       <c r="J26" s="18" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="K26" s="19" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L26" s="23" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M26" s="23" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N26" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O26" s="20" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P26" s="10" t="s">
         <v>34</v>
@@ -2849,46 +2873,46 @@
         <v>48</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>48</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>53</v>
+        <v>164</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>163</v>
+        <v>54</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="J27" s="18" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="K27" s="19" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L27" s="23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M27" s="23" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N27" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O27" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P27" s="10" t="s">
         <v>34</v>
@@ -2911,46 +2935,46 @@
         <v>48</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>48</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>54</v>
+        <v>171</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H28" s="7" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="J28" s="18" t="s">
         <v>41</v>
       </c>
       <c r="K28" s="19" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L28" s="23" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="M28" s="23" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="N28" s="23" t="s">
-        <v>175</v>
+        <v>45</v>
       </c>
       <c r="O28" s="20" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P28" s="10" t="s">
         <v>34</v>
@@ -2973,22 +2997,22 @@
         <v>48</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>48</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>64</v>
+        <v>178</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>39</v>
@@ -3000,19 +3024,19 @@
         <v>41</v>
       </c>
       <c r="K29" s="19" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L29" s="23" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M29" s="23" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="N29" s="23" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="O29" s="20" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="P29" s="10" t="s">
         <v>34</v>
@@ -3035,61 +3059,61 @@
         <v>48</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>48</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="E30" s="8" t="s">
         <v>23</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="I30" s="7" t="s">
         <v>27</v>
       </c>
       <c r="J30" s="18" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="K30" s="19" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L30" s="23" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M30" s="23" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="N30" s="23" t="s">
-        <v>45</v>
+        <v>189</v>
       </c>
       <c r="O30" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="P30" s="13" t="s">
-        <v>188</v>
+        <v>190</v>
+      </c>
+      <c r="P30" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="Q30" s="19" t="s">
-        <v>189</v>
+        <v>27</v>
       </c>
       <c r="R30" s="17" t="s">
-        <v>190</v>
+        <v>27</v>
       </c>
       <c r="S30" s="17" t="s">
-        <v>191</v>
+        <v>27</v>
       </c>
       <c r="T30" s="16" t="s">
-        <v>192</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31">
@@ -3097,61 +3121,61 @@
         <v>48</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>48</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="E31" s="8" t="s">
         <v>23</v>
       </c>
       <c r="F31" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I31" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J31" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="K31" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="L31" s="23" t="s">
         <v>193</v>
       </c>
-      <c r="G31" s="7" t="s">
+      <c r="M31" s="23" t="s">
         <v>194</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="J31" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="K31" s="19" t="s">
-        <v>195</v>
-      </c>
-      <c r="L31" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="M31" s="23" t="s">
-        <v>197</v>
       </c>
       <c r="N31" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O31" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="P31" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q31" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="R31" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="P31" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q31" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="R31" s="17" t="s">
-        <v>27</v>
-      </c>
       <c r="S31" s="17" t="s">
-        <v>27</v>
+        <v>199</v>
       </c>
       <c r="T31" s="16" t="s">
-        <v>27</v>
+        <v>200</v>
       </c>
     </row>
     <row r="32">
@@ -3159,10 +3183,10 @@
         <v>48</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>22</v>
@@ -3171,49 +3195,49 @@
         <v>23</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="I32" s="7" t="s">
         <v>27</v>
       </c>
       <c r="J32" s="18" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="K32" s="19" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="L32" s="23" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="M32" s="23" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="N32" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O32" s="20" t="s">
-        <v>200</v>
-      </c>
-      <c r="P32" s="13" t="s">
-        <v>188</v>
+        <v>206</v>
+      </c>
+      <c r="P32" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="Q32" s="19" t="s">
-        <v>201</v>
+        <v>27</v>
       </c>
       <c r="R32" s="17" t="s">
-        <v>202</v>
+        <v>27</v>
       </c>
       <c r="S32" s="17" t="s">
-        <v>191</v>
+        <v>27</v>
       </c>
       <c r="T32" s="16" t="s">
-        <v>203</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33">
@@ -3221,10 +3245,10 @@
         <v>48</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>22</v>
@@ -3233,158 +3257,158 @@
         <v>23</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="I33" s="7" t="s">
         <v>27</v>
       </c>
       <c r="J33" s="18" t="s">
-        <v>28</v>
+        <v>95</v>
       </c>
       <c r="K33" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="L33" s="23" t="s">
         <v>204</v>
       </c>
-      <c r="L33" s="23" t="s">
-        <v>196</v>
-      </c>
       <c r="M33" s="23" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="N33" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O33" s="20" t="s">
-        <v>205</v>
-      </c>
-      <c r="P33" s="12" t="s">
-        <v>120</v>
+        <v>208</v>
+      </c>
+      <c r="P33" s="13" t="s">
+        <v>196</v>
       </c>
       <c r="Q33" s="19" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="R33" s="17" t="s">
-        <v>122</v>
+        <v>210</v>
       </c>
       <c r="S33" s="17" t="s">
-        <v>123</v>
+        <v>199</v>
       </c>
       <c r="T33" s="16" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="B34" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="E34" s="10" t="s">
+      <c r="A34" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E34" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="F34" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="H34" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>211</v>
+      <c r="F34" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>27</v>
       </c>
       <c r="J34" s="18" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="K34" s="19" t="s">
         <v>212</v>
       </c>
       <c r="L34" s="23" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="M34" s="23" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="N34" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O34" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="P34" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q34" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="R34" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="S34" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="T34" s="16" t="s">
         <v>215</v>
-      </c>
-      <c r="P34" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q34" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="R34" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="S34" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="T34" s="16" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>23</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="J35" s="18" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="K35" s="19" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="L35" s="23" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="M35" s="23" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="N35" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O35" s="20" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>34</v>
@@ -3404,49 +3428,49 @@
     </row>
     <row r="36">
       <c r="A36" s="10" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>23</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>40</v>
+        <v>219</v>
       </c>
       <c r="J36" s="18" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="K36" s="19" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="L36" s="23" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="M36" s="23" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="N36" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O36" s="20" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="P36" s="10" t="s">
         <v>34</v>
@@ -3464,8 +3488,70 @@
         <v>27</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="I37" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J37" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="K37" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="L37" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="M37" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="N37" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O37" s="20" t="s">
+        <v>227</v>
+      </c>
+      <c r="P37" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q37" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R37" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S37" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T37" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="$A$1:$T$36"/>
+  <autoFilter ref="$A$1:$T$37"/>
   <pageSetup orientation="landscape" paperSize="9"/>
   <headerFooter>
     <oddHeader>&amp;R&amp;P</oddHeader>

--- a/threagile/output/stride/risks.xlsx
+++ b/threagile/output/stride/risks.xlsx
@@ -10,75 +10,75 @@
     <sheet name="VaultNote Threat Model" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'VaultNote Threat Model'!$A$1:$T$37</definedName>
+    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'VaultNote Threat Model'!$A$1:$T$68</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="331">
+  <si>
+    <t>STRIDE</t>
+  </si>
+  <si>
+    <t>Severity</t>
+  </si>
+  <si>
+    <t>CWE</t>
+  </si>
+  <si>
+    <t>Risk Category</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Check</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Likelihood</t>
+  </si>
+  <si>
+    <t>Impact</t>
+  </si>
+  <si>
+    <t>Function</t>
+  </si>
   <si>
     <t>Identified Risk</t>
   </si>
   <si>
+    <t>RAA %</t>
+  </si>
+  <si>
     <t>Status</t>
   </si>
   <si>
-    <t>STRIDE</t>
-  </si>
-  <si>
-    <t>Function</t>
-  </si>
-  <si>
-    <t>CWE</t>
-  </si>
-  <si>
-    <t>Risk Category</t>
+    <t>Justification</t>
+  </si>
+  <si>
+    <t>Checked by</t>
+  </si>
+  <si>
+    <t>Technical Asset</t>
   </si>
   <si>
     <t>Communication Link</t>
   </si>
   <si>
-    <t>RAA %</t>
+    <t>Mitigation</t>
+  </si>
+  <si>
+    <t>ID</t>
   </si>
   <si>
     <t>Ticket</t>
   </si>
   <si>
-    <t>Severity</t>
-  </si>
-  <si>
-    <t>Likelihood</t>
-  </si>
-  <si>
-    <t>Impact</t>
-  </si>
-  <si>
-    <t>Technical Asset</t>
-  </si>
-  <si>
-    <t>Action</t>
-  </si>
-  <si>
-    <t>Mitigation</t>
-  </si>
-  <si>
-    <t>Check</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Justification</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Checked by</t>
-  </si>
-  <si>
     <t>High</t>
   </si>
   <si>
@@ -103,7 +103,7 @@
     <t/>
   </si>
   <si>
-    <t>39</t>
+    <t>21</t>
   </si>
   <si>
     <t>Exposed Default Credentials: MinIO Object Storage is tagged as intentional-misconfiguration and stores confidential data</t>
@@ -144,7 +144,7 @@
     <t>PostgreSQL Connection</t>
   </si>
   <si>
-    <t>82</t>
+    <t>44</t>
   </si>
   <si>
     <t>SQL/NoSQL-Injection risk at API Server against database PostgreSQL Database via PostgreSQL Connection</t>
@@ -195,7 +195,7 @@
     <t>Nginx Reverse Proxy</t>
   </si>
   <si>
-    <t>2</t>
+    <t>1</t>
   </si>
   <si>
     <t>Lateral Movement via Shared Runtime on Docker Host: assets from 3 trust zones co-located</t>
@@ -237,6 +237,15 @@
     <t>missing-authentication@nginx-proxy&gt;http-to-api-server@nginx-proxy@api-server</t>
   </si>
   <si>
+    <t>Route to ECS API</t>
+  </si>
+  <si>
+    <t>Missing Authentication covering communication link Route to ECS API from AWS API Gateway to API Server</t>
+  </si>
+  <si>
+    <t>missing-authentication@aws-api-gateway&gt;route-to-ecs-api@aws-api-gateway@api-server</t>
+  </si>
+  <si>
     <t>Unlikely</t>
   </si>
   <si>
@@ -252,16 +261,28 @@
     <t>0</t>
   </si>
   <si>
+    <t>Missing Cloud Hardening (AWS) risk at AWS Cloud: CIS Benchmark for AWS</t>
+  </si>
+  <si>
+    <t>Cloud Hardening</t>
+  </si>
+  <si>
+    <t>Apply hardening of all cloud components and services, taking special care to follow the individual risk descriptions (which depend on the cloud provider tags in the model). &lt;br&gt;&lt;br&gt;For &lt;b&gt;Amazon Web Services (AWS)&lt;/b&gt;: Follow the &lt;i&gt;CIS Benchmark for Amazon Web Services&lt;/i&gt; (see also the automated checks of cloud audit tools like &lt;i&gt;"PacBot", "CloudSploit", "CloudMapper", "ScoutSuite", or "Prowler AWS CIS Benchmark Tool"&lt;/i&gt;). &lt;br&gt;For EC2 and other servers running Amazon Linux, follow the &lt;i&gt;CIS Benchmark for Amazon Linux&lt;/i&gt; and switch to IMDSv2. &lt;br&gt;For S3 buckets follow the &lt;i&gt;Security Best Practices for Amazon S3&lt;/i&gt; at &lt;a href="https://docs.aws.amazon.com/AmazonS3/latest/dev/security-best-practices.html"&gt;https://docs.aws.amazon.com/AmazonS3/latest/dev/security-best-practices.html&lt;/a&gt; to avoid accidental leakage. &lt;br&gt;Also take a look at some of these tools: &lt;a href="https://github.com/toniblyx/my-arsenal-of-aws-security-tools"&gt;https://github.com/toniblyx/my-arsenal-of-aws-security-tools&lt;/a&gt; &lt;br&gt;&lt;br&gt;For &lt;b&gt;Microsoft Azure&lt;/b&gt;: Follow the &lt;i&gt;CIS Benchmark for Microsoft Azure&lt;/i&gt; (see also the automated checks of cloud audit tools like &lt;i&gt;"CloudSploit" or "ScoutSuite"&lt;/i&gt;).&lt;br&gt;&lt;br&gt;For &lt;b&gt;Google Cloud Platform&lt;/b&gt;: Follow the &lt;i&gt;CIS Benchmark for Google Cloud Computing Platform&lt;/i&gt; (see also the automated checks of cloud audit tools like &lt;i&gt;"CloudSploit" or "ScoutSuite"&lt;/i&gt;). &lt;br&gt;&lt;br&gt;For &lt;b&gt;Oracle Cloud Platform&lt;/b&gt;: Follow the hardening best practices (see also the automated checks of cloud audit tools like &lt;i&gt;"CloudSploit"&lt;/i&gt;).</t>
+  </si>
+  <si>
+    <t>missing-cloud-hardening@aws-cloud@aws</t>
+  </si>
+  <si>
     <t>Missing Cloud Hardening risk at Docker Host</t>
   </si>
   <si>
-    <t>Cloud Hardening</t>
-  </si>
-  <si>
-    <t>Apply hardening of all cloud components and services, taking special care to follow the individual risk descriptions (which depend on the cloud provider tags in the model). &lt;br&gt;&lt;br&gt;For &lt;b&gt;Amazon Web Services (AWS)&lt;/b&gt;: Follow the &lt;i&gt;CIS Benchmark for Amazon Web Services&lt;/i&gt; (see also the automated checks of cloud audit tools like &lt;i&gt;"PacBot", "CloudSploit", "CloudMapper", "ScoutSuite", or "Prowler AWS CIS Benchmark Tool"&lt;/i&gt;). &lt;br&gt;For EC2 and other servers running Amazon Linux, follow the &lt;i&gt;CIS Benchmark for Amazon Linux&lt;/i&gt; and switch to IMDSv2. &lt;br&gt;For S3 buckets follow the &lt;i&gt;Security Best Practices for Amazon S3&lt;/i&gt; at &lt;a href="https://docs.aws.amazon.com/AmazonS3/latest/dev/security-best-practices.html"&gt;https://docs.aws.amazon.com/AmazonS3/latest/dev/security-best-practices.html&lt;/a&gt; to avoid accidental leakage. &lt;br&gt;Also take a look at some of these tools: &lt;a href="https://github.com/toniblyx/my-arsenal-of-aws-security-tools"&gt;https://github.com/toniblyx/my-arsenal-of-aws-security-tools&lt;/a&gt; &lt;br&gt;&lt;br&gt;For &lt;b&gt;Microsoft Azure&lt;/b&gt;: Follow the &lt;i&gt;CIS Benchmark for Microsoft Azure&lt;/i&gt; (see also the automated checks of cloud audit tools like &lt;i&gt;"CloudSploit" or "ScoutSuite"&lt;/i&gt;).&lt;br&gt;&lt;br&gt;For &lt;b&gt;Google Cloud Platform&lt;/b&gt;: Follow the &lt;i&gt;CIS Benchmark for Google Cloud Computing Platform&lt;/i&gt; (see also the automated checks of cloud audit tools like &lt;i&gt;"CloudSploit" or "ScoutSuite"&lt;/i&gt;). &lt;br&gt;&lt;br&gt;For &lt;b&gt;Oracle Cloud Platform&lt;/b&gt;: Follow the hardening best practices (see also the automated checks of cloud audit tools like &lt;i&gt;"CloudSploit"&lt;/i&gt;).</t>
-  </si>
-  <si>
     <t>missing-cloud-hardening@docker-host</t>
+  </si>
+  <si>
+    <t>Missing Cloud Hardening risk at External CI/CD</t>
+  </si>
+  <si>
+    <t>missing-cloud-hardening@external-cicd</t>
   </si>
   <si>
     <t>CWE-693</t>
@@ -293,7 +314,13 @@
     <t>Missing Hardening</t>
   </si>
   <si>
-    <t>Missing Hardening risk at API Server</t>
+    <t>AWS RDS PostgreSQL</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>Missing Hardening risk at AWS RDS PostgreSQL</t>
   </si>
   <si>
     <t>System Hardening</t>
@@ -302,73 +329,172 @@
     <t>Try to apply all hardening best practices (like CIS benchmarks, OWASP recommendations, vendor recommendations, DevSec Hardening Framework, DBSAT for Oracle databases, and others).</t>
   </si>
   <si>
-    <t>missing-hardening@api-server</t>
+    <t>missing-hardening@rds-postgresql</t>
+  </si>
+  <si>
+    <t>ECS Container Platform</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>Missing Hardening risk at ECS Container Platform</t>
+  </si>
+  <si>
+    <t>missing-hardening@ecs-platform</t>
   </si>
   <si>
     <t>PostgreSQL Database</t>
   </si>
   <si>
-    <t>100</t>
-  </si>
-  <si>
     <t>Missing Hardening risk at PostgreSQL Database</t>
   </si>
   <si>
     <t>missing-hardening@postgresql-db</t>
   </si>
   <si>
+    <t>CWE-22</t>
+  </si>
+  <si>
+    <t>Path-Traversal</t>
+  </si>
+  <si>
+    <t>MinIO File Storage</t>
+  </si>
+  <si>
+    <t>Path-Traversal risk at API Server against filesystem MinIO Object Storage via MinIO File Storage</t>
+  </si>
+  <si>
+    <t>Path-Traversal Prevention</t>
+  </si>
+  <si>
+    <t>Before accessing the file cross-check that it resides in the expected folder and is of the expected type and filename/suffix. Try to use a mapping if possible instead of directly accessing by a filename which is (partly or fully) provided by the caller. When a third-party product is used instead of custom developed software, check if the product applies the proper mitigation and ensure a reasonable patch-level.</t>
+  </si>
+  <si>
+    <t>path-traversal@api-server@minio-storage@api-server&gt;minio-file-storage</t>
+  </si>
+  <si>
+    <t>Pull Images from ECR</t>
+  </si>
+  <si>
+    <t>Path-Traversal risk at ECS Container Platform against filesystem AWS ECR Container Registry via Pull Images from ECR</t>
+  </si>
+  <si>
+    <t>path-traversal@ecs-platform@container-registry@ecs-platform&gt;pull-images-from-ecr</t>
+  </si>
+  <si>
+    <t>GitHub Actions Build Pipeline</t>
+  </si>
+  <si>
+    <t>Push Image to Registry</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Path-Traversal risk at GitHub Actions Build Pipeline against filesystem AWS ECR Container Registry via Push Image to Registry</t>
+  </si>
+  <si>
+    <t>path-traversal@build-pipeline@container-registry@build-pipeline&gt;push-image-to-registry</t>
+  </si>
+  <si>
+    <t>CWE-918</t>
+  </si>
+  <si>
+    <t>Server-Side Request Forgery (SSRF)</t>
+  </si>
+  <si>
+    <t>Server-Side Request Forgery (SSRF) risk at API Server server-side web-requesting the target MinIO Object Storage via MinIO File Storage</t>
+  </si>
+  <si>
+    <t>SSRF Prevention</t>
+  </si>
+  <si>
+    <t>Try to avoid constructing the outgoing target URL with caller controllable values. Alternatively use a mapping (whitelist) when accessing outgoing URLs instead of creating them including caller controllable values. When a third-party product is used instead of custom developed software, check if the product applies the proper mitigation and ensure a reasonable patch-level.</t>
+  </si>
+  <si>
+    <t>server-side-request-forgery@api-server@minio-storage@api-server&gt;minio-file-storage</t>
+  </si>
+  <si>
+    <t>Lambda Email Notifier</t>
+  </si>
+  <si>
+    <t>SES Email Send</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Server-Side Request Forgery (SSRF) risk at Lambda Email Notifier server-side web-requesting the target AWS SES via SES Email Send</t>
+  </si>
+  <si>
+    <t>server-side-request-forgery@lambda-notifier@aws-ses@lambda-notifier&gt;ses-email-send</t>
+  </si>
+  <si>
+    <t>Server-Side Request Forgery (SSRF) risk at ECS Container Platform server-side web-requesting the target AWS ECR Container Registry via Pull Images from ECR</t>
+  </si>
+  <si>
+    <t>server-side-request-forgery@ecs-platform@container-registry@ecs-platform&gt;pull-images-from-ecr</t>
+  </si>
+  <si>
+    <t>Server-Side Request Forgery (SSRF) risk at GitHub Actions Build Pipeline server-side web-requesting the target AWS ECR Container Registry via Push Image to Registry</t>
+  </si>
+  <si>
+    <t>server-side-request-forgery@build-pipeline@container-registry@build-pipeline&gt;push-image-to-registry</t>
+  </si>
+  <si>
+    <t>VaultNote Source Repository</t>
+  </si>
+  <si>
+    <t>Push to Pipeline</t>
+  </si>
+  <si>
+    <t>Server-Side Request Forgery (SSRF) risk at VaultNote Source Repository server-side web-requesting the target GitHub Actions Build Pipeline via Push to Pipeline</t>
+  </si>
+  <si>
+    <t>server-side-request-forgery@source-repo@build-pipeline@source-repo&gt;push-to-pipeline</t>
+  </si>
+  <si>
     <t>Low</t>
   </si>
   <si>
-    <t>Redis Cache</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>Missing Hardening risk at Redis Cache</t>
-  </si>
-  <si>
-    <t>missing-hardening@redis-cache</t>
-  </si>
-  <si>
-    <t>CWE-22</t>
-  </si>
-  <si>
-    <t>Path-Traversal</t>
-  </si>
-  <si>
-    <t>MinIO File Storage</t>
-  </si>
-  <si>
-    <t>Path-Traversal risk at API Server against filesystem MinIO Object Storage via MinIO File Storage</t>
-  </si>
-  <si>
-    <t>Path-Traversal Prevention</t>
-  </si>
-  <si>
-    <t>Before accessing the file cross-check that it resides in the expected folder and is of the expected type and filename/suffix. Try to use a mapping if possible instead of directly accessing by a filename which is (partly or fully) provided by the caller. When a third-party product is used instead of custom developed software, check if the product applies the proper mitigation and ensure a reasonable patch-level.</t>
-  </si>
-  <si>
-    <t>path-traversal@api-server@minio-storage@api-server&gt;minio-file-storage</t>
-  </si>
-  <si>
-    <t>CWE-918</t>
-  </si>
-  <si>
-    <t>Server-Side Request Forgery (SSRF)</t>
-  </si>
-  <si>
-    <t>Server-Side Request Forgery (SSRF) risk at API Server server-side web-requesting the target MinIO Object Storage via MinIO File Storage</t>
-  </si>
-  <si>
-    <t>SSRF Prevention</t>
-  </si>
-  <si>
-    <t>Try to avoid constructing the outgoing target URL with caller controllable values. Alternatively use a mapping (whitelist) when accessing outgoing URLs instead of creating them including caller controllable values. When a third-party product is used instead of custom developed software, check if the product applies the proper mitigation and ensure a reasonable patch-level.</t>
-  </si>
-  <si>
-    <t>server-side-request-forgery@api-server@minio-storage@api-server&gt;minio-file-storage</t>
+    <t>LLM Note Summarizer</t>
+  </si>
+  <si>
+    <t>Call RAG Pipeline</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Server-Side Request Forgery (SSRF) risk at LLM Note Summarizer server-side web-requesting the target Note RAG Pipeline via Call RAG Pipeline</t>
+  </si>
+  <si>
+    <t>server-side-request-forgery@llm-summarizer@rag-pipeline@llm-summarizer&gt;call-rag-pipeline</t>
+  </si>
+  <si>
+    <t>Query Vector Store</t>
+  </si>
+  <si>
+    <t>Server-Side Request Forgery (SSRF) risk at LLM Note Summarizer server-side web-requesting the target VaultNote Vector Store via Query Vector Store</t>
+  </si>
+  <si>
+    <t>server-side-request-forgery@llm-summarizer@vector-store@llm-summarizer&gt;query-vector-store</t>
+  </si>
+  <si>
+    <t>Note RAG Pipeline</t>
+  </si>
+  <si>
+    <t>Retrieve from Vector Store</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Server-Side Request Forgery (SSRF) risk at Note RAG Pipeline server-side web-requesting the target VaultNote Vector Store via Retrieve from Vector Store</t>
+  </si>
+  <si>
+    <t>server-side-request-forgery@rag-pipeline@vector-store@rag-pipeline&gt;retrieve-from-vector-store</t>
   </si>
   <si>
     <t>CWE-319</t>
@@ -426,6 +552,57 @@
     <t>CWE-501</t>
   </si>
   <si>
+    <t>Unguarded Access From Internet</t>
+  </si>
+  <si>
+    <t>Unguarded Access from Internet of API Server by AWS API Gateway via Route to ECS API</t>
+  </si>
+  <si>
+    <t>Encapsulation of Technical Asset</t>
+  </si>
+  <si>
+    <t>Encapsulate the asset behind a guarding service, application, or reverse-proxy. For admin maintenance a bastion-host should be used as a jump-server. For file transfer a store-and-forward-host should be used as an indirect file exchange platform.</t>
+  </si>
+  <si>
+    <t>unguarded-access-from-internet@api-server@aws-api-gateway@aws-api-gateway&gt;route-to-ecs-api</t>
+  </si>
+  <si>
+    <t>AWS ECR Container Registry</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Unguarded Access from Internet of AWS ECR Container Registry by GitHub Actions Build Pipeline via Push Image to Registry</t>
+  </si>
+  <si>
+    <t>unguarded-access-from-internet@container-registry@build-pipeline@build-pipeline&gt;push-image-to-registry</t>
+  </si>
+  <si>
+    <t>Unguarded Access from Internet of GitHub Actions Build Pipeline by VaultNote Source Repository via Push to Pipeline</t>
+  </si>
+  <si>
+    <t>unguarded-access-from-internet@build-pipeline@source-repo@source-repo&gt;push-to-pipeline</t>
+  </si>
+  <si>
+    <t>Unguarded Access from Internet of Note RAG Pipeline by LLM Note Summarizer via Call RAG Pipeline</t>
+  </si>
+  <si>
+    <t>unguarded-access-from-internet@rag-pipeline@llm-summarizer@llm-summarizer&gt;call-rag-pipeline</t>
+  </si>
+  <si>
+    <t>VaultNote Vector Store</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Unguarded Access from Internet of VaultNote Vector Store by LLM Note Summarizer via Query Vector Store</t>
+  </si>
+  <si>
+    <t>unguarded-access-from-internet@vector-store@llm-summarizer@llm-summarizer&gt;query-vector-store</t>
+  </si>
+  <si>
     <t>Unguarded Direct Datastore Access</t>
   </si>
   <si>
@@ -441,21 +618,69 @@
     <t>unguarded-direct-datastore-access@api-server&gt;postgresql-connection@api-server@postgresql-db</t>
   </si>
   <si>
+    <t>Unguarded Direct Datastore Access of MinIO Object Storage by API Server via MinIO File Storage</t>
+  </si>
+  <si>
+    <t>unguarded-direct-datastore-access@api-server&gt;minio-file-storage@api-server@minio-storage</t>
+  </si>
+  <si>
+    <t>Redis Cache</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
     <t>Unguarded Direct Datastore Access of Redis Cache by API Server via Redis Session Store</t>
   </si>
   <si>
     <t>unguarded-direct-datastore-access@api-server&gt;redis-session-store@api-server@redis-cache</t>
   </si>
   <si>
-    <t>Unguarded Direct Datastore Access of MinIO Object Storage by API Server via MinIO File Storage</t>
-  </si>
-  <si>
-    <t>unguarded-direct-datastore-access@api-server&gt;minio-file-storage@api-server@minio-storage</t>
+    <t>CWE-200</t>
+  </si>
+  <si>
+    <t>Accidental Secret Leak</t>
+  </si>
+  <si>
+    <t>Accidental Secret Leak(Git) risk at VaultNote Source Repository: Git Leak Prevention</t>
+  </si>
+  <si>
+    <t>Build Pipeline Hardening</t>
+  </si>
+  <si>
+    <t>Establish measures preventing accidental check-in or package-in of secrets into sourcecode repositories and artifact registries. This starts by using good .gitignore and .dockerignore files, but does not stop there. See for example tools like &lt;i&gt;\"git-secrets\"&lt;/i&gt; or &lt;i&gt;\"Talisman\"&lt;/i&gt; to have check-in preventive measures for secrets. Consider also to regularly scan your repositories for secrets accidentally checked-in using scanning tools like &lt;i&gt;"gitleaks"&lt;/i&gt; or &lt;i&gt;"gitrob"&lt;/i&gt;.</t>
+  </si>
+  <si>
+    <t>accidental-secret-leak@source-repo</t>
   </si>
   <si>
     <t>CWE-912</t>
   </si>
   <si>
+    <t>Code Backdooring</t>
+  </si>
+  <si>
+    <t>Code Backdooring risk at AWS ECR Container Registry</t>
+  </si>
+  <si>
+    <t>Reduce the attack surface of backdooring the build pipeline by not directly exposing the build pipeline components on the public internet and also not exposing it in front of unmanaged (out-of-scope) developer clients.Also consider the use of code signing to prevent code modifications.</t>
+  </si>
+  <si>
+    <t>code-backdooring@container-registry</t>
+  </si>
+  <si>
+    <t>Code Backdooring risk at GitHub Actions Build Pipeline</t>
+  </si>
+  <si>
+    <t>code-backdooring@build-pipeline</t>
+  </si>
+  <si>
+    <t>Code Backdooring risk at VaultNote Source Repository</t>
+  </si>
+  <si>
+    <t>code-backdooring@source-repo</t>
+  </si>
+  <si>
     <t>Container Base Image Backdooring</t>
   </si>
   <si>
@@ -492,12 +717,39 @@
     <t>container-baseimage-backdooring@minio-storage</t>
   </si>
   <si>
+    <t>Container Base Image Backdooring risk at Note RAG Pipeline</t>
+  </si>
+  <si>
+    <t>container-baseimage-backdooring@rag-pipeline</t>
+  </si>
+  <si>
     <t>Container Base Image Backdooring risk at Redis Cache</t>
   </si>
   <si>
     <t>container-baseimage-backdooring@redis-cache</t>
   </si>
   <si>
+    <t>Container Base Image Backdooring risk at VaultNote Vector Store</t>
+  </si>
+  <si>
+    <t>container-baseimage-backdooring@vector-store</t>
+  </si>
+  <si>
+    <t>Container Platform Escape</t>
+  </si>
+  <si>
+    <t>Container Platform Escape risk at ECS Container Platform</t>
+  </si>
+  <si>
+    <t>Apply hardening of all container infrastructures. &lt;p&gt;See for example the &lt;i&gt;CIS-Benchmarks for Docker and Kubernetes&lt;/i&gt; as well as the &lt;i&gt;Docker Bench for Security&lt;/i&gt; ( &lt;a href="https://github.com/docker/docker-bench-security"&gt;https://github.com/docker/docker-bench-security&lt;/a&gt; ) or &lt;i&gt;InSpec Checks for Docker and Kubernetes&lt;/i&gt; ( &lt;a href="https://github.com/dev-sec/cis-kubernetes-benchmark"&gt;https://github.com/dev-sec/cis-docker-benchmark&lt;/a&gt; and &lt;a href="https://github.com/dev-sec/cis-kubernetes-benchmark"&gt;https://github.com/dev-sec/cis-kubernetes-benchmark&lt;/a&gt; ). Use only trusted base images, verify digital signatures and apply image creation best practices. Also consider using Google's &lt;b&gt;Distroless&lt;/i&gt; base images or otherwise very small base images. Apply namespace isolation and nod affinity to separate pods from each other in terms of access and nodes the same style as you separate data.</t>
+  </si>
+  <si>
+    <t>Are recommendations from the linked cheat sheet and referenced ASVS or CSVS chapter applied?</t>
+  </si>
+  <si>
+    <t>container-platform-escape@ecs-platform</t>
+  </si>
+  <si>
     <t>CWE-1127</t>
   </si>
   <si>
@@ -505,9 +757,6 @@
   </si>
   <si>
     <t>Missing Build Infrastructure in the threat model (referencing asset API Server as an example)</t>
-  </si>
-  <si>
-    <t>Build Pipeline Hardening</t>
   </si>
   <si>
     <t>Include the build infrastructure in the model.</t>
@@ -628,19 +877,58 @@
     <t>VAULT-95</t>
   </si>
   <si>
+    <t>Unchecked Deployment</t>
+  </si>
+  <si>
+    <t>Unchecked Deployment risk at GitHub Actions Build Pipeline</t>
+  </si>
+  <si>
+    <t>Apply DevSecOps best-practices and use scanning tools to identify vulnerabilities in source- or byte-code,dependencies, container layers, and optionally also via dynamic scans against running test systems.</t>
+  </si>
+  <si>
+    <t>unchecked-deployment@build-pipeline</t>
+  </si>
+  <si>
+    <t>Unchecked Deployment risk at VaultNote Source Repository</t>
+  </si>
+  <si>
+    <t>unchecked-deployment@source-repo</t>
+  </si>
+  <si>
+    <t>Unchecked Deployment risk at AWS ECR Container Registry</t>
+  </si>
+  <si>
+    <t>unchecked-deployment@container-registry</t>
+  </si>
+  <si>
     <t>CWE-311</t>
   </si>
   <si>
     <t>Unencrypted Technical Assets</t>
   </si>
   <si>
+    <t>Unencrypted Technical Asset named AWS RDS PostgreSQL missing end user individual encryption with data-with-end-user-individual-key</t>
+  </si>
+  <si>
+    <t>Encryption of Technical Asset</t>
+  </si>
+  <si>
+    <t>Apply encryption to the technical asset.</t>
+  </si>
+  <si>
+    <t>unencrypted-asset@rds-postgresql</t>
+  </si>
+  <si>
+    <t>AWS S3 Notes Bucket</t>
+  </si>
+  <si>
+    <t>Unencrypted Technical Asset named AWS S3 Notes Bucket</t>
+  </si>
+  <si>
+    <t>unencrypted-asset@s3-notes-bucket</t>
+  </si>
+  <si>
     <t>Unencrypted Technical Asset named Redis Cache</t>
-  </si>
-  <si>
-    <t>Encryption of Technical Asset</t>
-  </si>
-  <si>
-    <t>Apply encryption to the technical asset.</t>
   </si>
   <si>
     <t>unencrypted-asset@redis-cache</t>
@@ -709,6 +997,27 @@
   </si>
   <si>
     <t>dos-risky-access-across-trust-boundary@postgresql-db@api-server@api-server&gt;postgresql-connection-&gt;</t>
+  </si>
+  <si>
+    <t>Unnecessary Technical Asset</t>
+  </si>
+  <si>
+    <t>Unnecessary Technical Asset named AWS RDS PostgreSQL</t>
+  </si>
+  <si>
+    <t>Attack Surface Reduction</t>
+  </si>
+  <si>
+    <t>Try to avoid using technical assets that do not process or store anything.</t>
+  </si>
+  <si>
+    <t>unnecessary-technical-asset@rds-postgresql</t>
+  </si>
+  <si>
+    <t>Unnecessary Technical Asset named AWS S3 Notes Bucket</t>
+  </si>
+  <si>
+    <t>unnecessary-technical-asset@s3-notes-bucket</t>
   </si>
 </sst>
 </file>
@@ -1241,8 +1550,8 @@
     <col customWidth="true" max="5" min="5" width="17.857142857142854"/>
     <col customWidth="true" max="6" min="6" width="13.571428571428571"/>
     <col customWidth="true" max="7" min="7" width="55.57142857142857"/>
-    <col customWidth="true" max="8" min="8" width="23.857142857142858"/>
-    <col customWidth="true" max="9" min="9" width="25"/>
+    <col customWidth="true" max="8" min="8" width="31.57142857142857"/>
+    <col customWidth="true" max="9" min="9" width="29"/>
     <col customWidth="true" max="10" min="10" width="12"/>
     <col customWidth="true" max="11" min="11" width="75"/>
     <col customWidth="true" max="12" min="12" width="66.42857142857143"/>
@@ -1258,64 +1567,64 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="F1" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="24" t="s">
+      <c r="L1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="M1" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="N1" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="24" t="s">
+      <c r="O1" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="P1" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="24" t="s">
+      <c r="Q1" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="R1" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="L1" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" s="24" t="s">
+      <c r="S1" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="N1" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="O1" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="P1" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q1" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="R1" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="S1" s="24" t="s">
+      <c r="T1" s="24" t="s">
         <v>19</v>
-      </c>
-      <c r="T1" s="24" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2">
@@ -1633,46 +1942,46 @@
         <v>47</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="J7" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K7" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J7" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="K7" s="19" t="s">
-        <v>77</v>
-      </c>
       <c r="L7" s="23" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="M7" s="23" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="N7" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O7" s="20" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="P7" s="10" t="s">
         <v>34</v>
@@ -1695,46 +2004,46 @@
         <v>47</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>23</v>
       </c>
       <c r="F8" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="K8" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="L8" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="M8" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="H8" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J8" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="K8" s="19" t="s">
+      <c r="N8" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O8" s="20" t="s">
         <v>83</v>
-      </c>
-      <c r="L8" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="M8" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="N8" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="O8" s="20" t="s">
-        <v>87</v>
       </c>
       <c r="P8" s="10" t="s">
         <v>34</v>
@@ -1757,10 +2066,10 @@
         <v>47</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>35</v>
@@ -1769,34 +2078,34 @@
         <v>23</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J9" s="18" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="K9" s="19" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L9" s="23" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="M9" s="23" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="N9" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O9" s="20" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="P9" s="10" t="s">
         <v>34</v>
@@ -1815,50 +2124,50 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" s="6" t="s">
+      <c r="A10" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="I10" s="5" t="s">
+      <c r="F10" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10" s="7" t="s">
         <v>27</v>
       </c>
       <c r="J10" s="18" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="K10" s="19" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L10" s="23" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="M10" s="23" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="N10" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O10" s="20" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="P10" s="10" t="s">
         <v>34</v>
@@ -1877,38 +2186,38 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B11" s="8" t="s">
+      <c r="A11" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="8" t="s">
+      <c r="C11" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="H11" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="I11" s="7" t="s">
+      <c r="H11" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="I11" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J11" s="18" t="s">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="K11" s="19" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="L11" s="23" t="s">
         <v>91</v>
@@ -1917,10 +2226,10 @@
         <v>92</v>
       </c>
       <c r="N11" s="23" t="s">
-        <v>45</v>
+        <v>93</v>
       </c>
       <c r="O11" s="20" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="P11" s="10" t="s">
         <v>34</v>
@@ -1943,46 +2252,46 @@
         <v>47</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>48</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>39</v>
+        <v>97</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>105</v>
+        <v>27</v>
       </c>
       <c r="J12" s="18" t="s">
-        <v>41</v>
+        <v>98</v>
       </c>
       <c r="K12" s="19" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="L12" s="23" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="M12" s="23" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="N12" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O12" s="20" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="P12" s="10" t="s">
         <v>34</v>
@@ -2011,40 +2320,40 @@
         <v>48</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="I13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J13" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="K13" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="J13" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="K13" s="19" t="s">
-        <v>112</v>
-      </c>
       <c r="L13" s="23" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="M13" s="23" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="N13" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O13" s="20" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="P13" s="10" t="s">
         <v>34</v>
@@ -2070,43 +2379,43 @@
         <v>52</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>23</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>105</v>
+        <v>27</v>
       </c>
       <c r="J14" s="18" t="s">
-        <v>41</v>
+        <v>98</v>
       </c>
       <c r="K14" s="19" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="L14" s="23" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="M14" s="23" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="N14" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O14" s="20" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="P14" s="10" t="s">
         <v>34</v>
@@ -2129,46 +2438,46 @@
         <v>47</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>39</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>40</v>
+        <v>112</v>
       </c>
       <c r="J15" s="18" t="s">
         <v>41</v>
       </c>
       <c r="K15" s="19" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="L15" s="23" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="M15" s="23" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="N15" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O15" s="20" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="P15" s="10" t="s">
         <v>34</v>
@@ -2194,43 +2503,43 @@
         <v>52</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="G16" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="I16" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="H16" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>49</v>
-      </c>
       <c r="J16" s="18" t="s">
-        <v>41</v>
+        <v>104</v>
       </c>
       <c r="K16" s="19" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="L16" s="23" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="M16" s="23" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="N16" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O16" s="20" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="P16" s="10" t="s">
         <v>34</v>
@@ -2262,52 +2571,52 @@
         <v>22</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>57</v>
+        <v>120</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>67</v>
+        <v>121</v>
       </c>
       <c r="J17" s="18" t="s">
-        <v>58</v>
+        <v>122</v>
       </c>
       <c r="K17" s="19" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="L17" s="23" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="M17" s="23" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="N17" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O17" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="P17" s="12" t="s">
-        <v>128</v>
+        <v>124</v>
+      </c>
+      <c r="P17" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="Q17" s="19" t="s">
-        <v>129</v>
+        <v>27</v>
       </c>
       <c r="R17" s="17" t="s">
-        <v>130</v>
+        <v>27</v>
       </c>
       <c r="S17" s="17" t="s">
-        <v>131</v>
+        <v>27</v>
       </c>
       <c r="T17" s="16" t="s">
-        <v>132</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18">
@@ -2321,40 +2630,40 @@
         <v>48</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>40</v>
+        <v>112</v>
       </c>
       <c r="J18" s="18" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="K18" s="19" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="L18" s="23" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="M18" s="23" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="N18" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O18" s="20" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="P18" s="10" t="s">
         <v>34</v>
@@ -2383,40 +2692,40 @@
         <v>48</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="F19" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="J19" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="K19" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="H19" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="J19" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="K19" s="19" t="s">
-        <v>139</v>
-      </c>
       <c r="L19" s="23" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="M19" s="23" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="N19" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O19" s="20" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="P19" s="10" t="s">
         <v>34</v>
@@ -2439,46 +2748,46 @@
         <v>48</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="J20" s="18" t="s">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="K20" s="19" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="L20" s="23" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="M20" s="23" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="N20" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O20" s="20" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="P20" s="10" t="s">
         <v>34</v>
@@ -2501,46 +2810,46 @@
         <v>48</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>39</v>
+        <v>120</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>27</v>
+        <v>121</v>
       </c>
       <c r="J21" s="18" t="s">
-        <v>41</v>
+        <v>122</v>
       </c>
       <c r="K21" s="19" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="L21" s="23" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="M21" s="23" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="N21" s="23" t="s">
-        <v>148</v>
+        <v>45</v>
       </c>
       <c r="O21" s="20" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="P21" s="10" t="s">
         <v>34</v>
@@ -2563,46 +2872,46 @@
         <v>48</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F22" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="J22" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="K22" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="L22" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="M22" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="N22" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O22" s="20" t="s">
         <v>143</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="J22" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="K22" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="L22" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="M22" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="N22" s="23" t="s">
-        <v>148</v>
-      </c>
-      <c r="O22" s="20" t="s">
-        <v>151</v>
       </c>
       <c r="P22" s="10" t="s">
         <v>34</v>
@@ -2625,46 +2934,46 @@
         <v>48</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>94</v>
+        <v>145</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>27</v>
+        <v>146</v>
       </c>
       <c r="J23" s="18" t="s">
-        <v>95</v>
+        <v>147</v>
       </c>
       <c r="K23" s="19" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L23" s="23" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="M23" s="23" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="N23" s="23" t="s">
-        <v>148</v>
+        <v>45</v>
       </c>
       <c r="O23" s="20" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="P23" s="10" t="s">
         <v>34</v>
@@ -2687,46 +2996,46 @@
         <v>48</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>26</v>
+        <v>145</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>27</v>
+        <v>150</v>
       </c>
       <c r="J24" s="18" t="s">
-        <v>28</v>
+        <v>147</v>
       </c>
       <c r="K24" s="19" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="L24" s="23" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="M24" s="23" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="N24" s="23" t="s">
-        <v>148</v>
+        <v>45</v>
       </c>
       <c r="O24" s="20" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="P24" s="10" t="s">
         <v>34</v>
@@ -2749,43 +3058,43 @@
         <v>48</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>99</v>
+        <v>153</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>27</v>
+        <v>154</v>
       </c>
       <c r="J25" s="18" t="s">
-        <v>100</v>
+        <v>155</v>
       </c>
       <c r="K25" s="19" t="s">
         <v>156</v>
       </c>
       <c r="L25" s="23" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="M25" s="23" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="N25" s="23" t="s">
-        <v>148</v>
+        <v>45</v>
       </c>
       <c r="O25" s="20" t="s">
         <v>157</v>
@@ -2807,32 +3116,32 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F26" s="8" t="s">
+      <c r="A26" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F26" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="G26" s="7" t="s">
+      <c r="G26" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="H26" s="7" t="s">
+      <c r="H26" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="I26" s="7" t="s">
-        <v>27</v>
+      <c r="I26" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="J26" s="18" t="s">
         <v>41</v>
@@ -2869,50 +3178,50 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D27" s="8" t="s">
+      <c r="A27" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J27" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K27" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="E27" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="J27" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="K27" s="19" t="s">
-        <v>167</v>
-      </c>
       <c r="L27" s="23" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="M27" s="23" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="N27" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O27" s="20" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="P27" s="10" t="s">
         <v>34</v>
@@ -2931,50 +3240,50 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="H28" s="7" t="s">
+      <c r="A28" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="H28" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="I28" s="7" t="s">
-        <v>67</v>
+      <c r="I28" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="J28" s="18" t="s">
         <v>41</v>
       </c>
       <c r="K28" s="19" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="L28" s="23" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="M28" s="23" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="N28" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O28" s="20" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="P28" s="10" t="s">
         <v>34</v>
@@ -2993,112 +3302,112 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B29" s="8" t="s">
+      <c r="A29" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J29" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="K29" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="L29" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="M29" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="N29" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O29" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="P29" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q29" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="R29" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="S29" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="T29" s="16" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I30" s="5" t="s">
         <v>72</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="J29" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="K29" s="19" t="s">
-        <v>180</v>
-      </c>
-      <c r="L29" s="23" t="s">
-        <v>181</v>
-      </c>
-      <c r="M29" s="23" t="s">
-        <v>182</v>
-      </c>
-      <c r="N29" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="O29" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="P29" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q29" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="R29" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="S29" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="T29" s="16" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="I30" s="7" t="s">
-        <v>27</v>
       </c>
       <c r="J30" s="18" t="s">
         <v>41</v>
       </c>
       <c r="K30" s="19" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="L30" s="23" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="M30" s="23" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="N30" s="23" t="s">
-        <v>189</v>
+        <v>45</v>
       </c>
       <c r="O30" s="20" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="P30" s="10" t="s">
         <v>34</v>
@@ -3121,61 +3430,61 @@
         <v>48</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>72</v>
+        <v>21</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>64</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>74</v>
+        <v>175</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>27</v>
+        <v>181</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>27</v>
+        <v>121</v>
       </c>
       <c r="J31" s="18" t="s">
-        <v>76</v>
+        <v>182</v>
       </c>
       <c r="K31" s="19" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="L31" s="23" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="M31" s="23" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="N31" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O31" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="P31" s="13" t="s">
-        <v>196</v>
+        <v>184</v>
+      </c>
+      <c r="P31" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="Q31" s="19" t="s">
-        <v>197</v>
+        <v>27</v>
       </c>
       <c r="R31" s="17" t="s">
-        <v>198</v>
+        <v>27</v>
       </c>
       <c r="S31" s="17" t="s">
-        <v>199</v>
+        <v>27</v>
       </c>
       <c r="T31" s="16" t="s">
-        <v>200</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32">
@@ -3183,46 +3492,46 @@
         <v>48</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>72</v>
+        <v>21</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>201</v>
+        <v>175</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>27</v>
+        <v>141</v>
       </c>
       <c r="J32" s="18" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="K32" s="19" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="L32" s="23" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="M32" s="23" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
       <c r="N32" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O32" s="20" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="P32" s="10" t="s">
         <v>34</v>
@@ -3245,61 +3554,61 @@
         <v>48</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>72</v>
+        <v>21</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>201</v>
+        <v>175</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>94</v>
+        <v>153</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>27</v>
+        <v>146</v>
       </c>
       <c r="J33" s="18" t="s">
-        <v>95</v>
+        <v>155</v>
       </c>
       <c r="K33" s="19" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
       <c r="L33" s="23" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="M33" s="23" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
       <c r="N33" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O33" s="20" t="s">
-        <v>208</v>
-      </c>
-      <c r="P33" s="13" t="s">
-        <v>196</v>
+        <v>188</v>
+      </c>
+      <c r="P33" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="Q33" s="19" t="s">
-        <v>209</v>
+        <v>27</v>
       </c>
       <c r="R33" s="17" t="s">
-        <v>210</v>
+        <v>27</v>
       </c>
       <c r="S33" s="17" t="s">
-        <v>199</v>
+        <v>27</v>
       </c>
       <c r="T33" s="16" t="s">
-        <v>211</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34">
@@ -3307,108 +3616,108 @@
         <v>48</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>72</v>
+        <v>21</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>201</v>
+        <v>175</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>27</v>
+        <v>150</v>
       </c>
       <c r="J34" s="18" t="s">
-        <v>28</v>
+        <v>190</v>
       </c>
       <c r="K34" s="19" t="s">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="L34" s="23" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="M34" s="23" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
       <c r="N34" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O34" s="20" t="s">
-        <v>213</v>
-      </c>
-      <c r="P34" s="12" t="s">
-        <v>128</v>
+        <v>192</v>
+      </c>
+      <c r="P34" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="Q34" s="19" t="s">
-        <v>214</v>
+        <v>27</v>
       </c>
       <c r="R34" s="17" t="s">
-        <v>130</v>
+        <v>27</v>
       </c>
       <c r="S34" s="17" t="s">
-        <v>131</v>
+        <v>27</v>
       </c>
       <c r="T34" s="16" t="s">
-        <v>215</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="s">
+      <c r="A35" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J35" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="B35" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="F35" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="J35" s="18" t="s">
-        <v>41</v>
-      </c>
       <c r="K35" s="19" t="s">
-        <v>220</v>
+        <v>194</v>
       </c>
       <c r="L35" s="23" t="s">
-        <v>221</v>
+        <v>195</v>
       </c>
       <c r="M35" s="23" t="s">
-        <v>222</v>
+        <v>196</v>
       </c>
       <c r="N35" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O35" s="20" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>34</v>
@@ -3427,50 +3736,50 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="B36" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="F36" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="H36" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="I36" s="9" t="s">
-        <v>219</v>
+      <c r="A36" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="J36" s="18" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="K36" s="19" t="s">
-        <v>224</v>
+        <v>198</v>
       </c>
       <c r="L36" s="23" t="s">
-        <v>221</v>
+        <v>195</v>
       </c>
       <c r="M36" s="23" t="s">
-        <v>222</v>
+        <v>196</v>
       </c>
       <c r="N36" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O36" s="20" t="s">
-        <v>225</v>
+        <v>199</v>
       </c>
       <c r="P36" s="10" t="s">
         <v>34</v>
@@ -3489,69 +3798,1991 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="F37" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="G37" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="I37" s="9" t="s">
-        <v>40</v>
+      <c r="A37" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>49</v>
       </c>
       <c r="J37" s="18" t="s">
-        <v>95</v>
+        <v>201</v>
       </c>
       <c r="K37" s="19" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="L37" s="23" t="s">
-        <v>221</v>
+        <v>195</v>
       </c>
       <c r="M37" s="23" t="s">
-        <v>222</v>
+        <v>196</v>
       </c>
       <c r="N37" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O37" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="P37" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q37" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R37" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S37" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T37" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="I38" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J38" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="K38" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="L38" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="M38" s="23" t="s">
+        <v>208</v>
+      </c>
+      <c r="N38" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O38" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="P38" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q38" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R38" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S38" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T38" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="I39" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J39" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="K39" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="L39" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="M39" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="N39" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O39" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="P39" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q39" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R39" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S39" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T39" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="H40" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="I40" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J40" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="K40" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="L40" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="M40" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="N40" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O40" s="20" t="s">
+        <v>216</v>
+      </c>
+      <c r="P40" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q40" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R40" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S40" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T40" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J41" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="K41" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="L41" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="M41" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="N41" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O41" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="P41" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q41" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R41" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S41" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T41" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="H42" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I42" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J42" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K42" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="L42" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="M42" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="N42" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="O42" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="P42" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q42" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R42" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S42" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T42" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="H43" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="I43" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J43" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="K43" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="L43" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="M43" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="N43" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="O43" s="20" t="s">
+        <v>226</v>
+      </c>
+      <c r="P43" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q43" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R43" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S43" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T43" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I44" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J44" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="K44" s="19" t="s">
         <v>227</v>
       </c>
-      <c r="P37" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q37" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="R37" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="S37" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="T37" s="16" t="s">
+      <c r="L44" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="M44" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="N44" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="O44" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="P44" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q44" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R44" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S44" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T44" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I45" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J45" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K45" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="L45" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="M45" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="N45" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="O45" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="P45" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q45" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R45" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S45" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T45" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="I46" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J46" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="K46" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="L46" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="M46" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="N46" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="O46" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="P46" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q46" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R46" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S46" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T46" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="I47" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J47" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="K47" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="L47" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="M47" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="N47" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="O47" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="P47" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q47" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R47" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S47" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T47" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="H48" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="I48" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J48" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="K48" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="L48" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="M48" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="N48" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="O48" s="20" t="s">
+        <v>236</v>
+      </c>
+      <c r="P48" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q48" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R48" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S48" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T48" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="I49" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J49" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="K49" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="L49" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="M49" s="23" t="s">
+        <v>239</v>
+      </c>
+      <c r="N49" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="O49" s="20" t="s">
+        <v>241</v>
+      </c>
+      <c r="P49" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q49" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R49" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S49" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T49" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="H50" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I50" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J50" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K50" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="L50" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="M50" s="23" t="s">
+        <v>245</v>
+      </c>
+      <c r="N50" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O50" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="P50" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q50" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R50" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S50" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T50" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="H51" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="I51" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J51" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="K51" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="L51" s="23" t="s">
+        <v>251</v>
+      </c>
+      <c r="M51" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="N51" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O51" s="20" t="s">
+        <v>253</v>
+      </c>
+      <c r="P51" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q51" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R51" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S51" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T51" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="H52" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I52" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="J52" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K52" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="L52" s="23" t="s">
+        <v>258</v>
+      </c>
+      <c r="M52" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="N52" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O52" s="20" t="s">
+        <v>260</v>
+      </c>
+      <c r="P52" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q52" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R52" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S52" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T52" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="G53" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="H53" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I53" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J53" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K53" s="19" t="s">
+        <v>263</v>
+      </c>
+      <c r="L53" s="23" t="s">
+        <v>264</v>
+      </c>
+      <c r="M53" s="23" t="s">
+        <v>265</v>
+      </c>
+      <c r="N53" s="23" t="s">
+        <v>266</v>
+      </c>
+      <c r="O53" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="P53" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q53" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R53" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S53" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T53" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="H54" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I54" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J54" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K54" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="L54" s="23" t="s">
+        <v>270</v>
+      </c>
+      <c r="M54" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="N54" s="23" t="s">
+        <v>272</v>
+      </c>
+      <c r="O54" s="20" t="s">
+        <v>273</v>
+      </c>
+      <c r="P54" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q54" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R54" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S54" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T54" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="G55" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="H55" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I55" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J55" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="K55" s="19" t="s">
+        <v>275</v>
+      </c>
+      <c r="L55" s="23" t="s">
+        <v>276</v>
+      </c>
+      <c r="M55" s="23" t="s">
+        <v>277</v>
+      </c>
+      <c r="N55" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O55" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="P55" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="Q55" s="19" t="s">
+        <v>280</v>
+      </c>
+      <c r="R55" s="17" t="s">
+        <v>281</v>
+      </c>
+      <c r="S55" s="17" t="s">
+        <v>282</v>
+      </c>
+      <c r="T55" s="16" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="G56" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="H56" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="I56" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J56" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="K56" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="L56" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="M56" s="23" t="s">
+        <v>286</v>
+      </c>
+      <c r="N56" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O56" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="P56" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q56" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R56" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S56" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T56" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="G57" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="H57" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="I57" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J57" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="K57" s="19" t="s">
+        <v>288</v>
+      </c>
+      <c r="L57" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="M57" s="23" t="s">
+        <v>286</v>
+      </c>
+      <c r="N57" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O57" s="20" t="s">
+        <v>289</v>
+      </c>
+      <c r="P57" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q57" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R57" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S57" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T57" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F58" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="G58" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="H58" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="I58" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J58" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="K58" s="19" t="s">
+        <v>290</v>
+      </c>
+      <c r="L58" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="M58" s="23" t="s">
+        <v>286</v>
+      </c>
+      <c r="N58" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O58" s="20" t="s">
+        <v>291</v>
+      </c>
+      <c r="P58" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q58" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R58" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S58" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T58" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="G59" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="H59" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="I59" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J59" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="K59" s="19" t="s">
+        <v>294</v>
+      </c>
+      <c r="L59" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="M59" s="23" t="s">
+        <v>296</v>
+      </c>
+      <c r="N59" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O59" s="20" t="s">
+        <v>297</v>
+      </c>
+      <c r="P59" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q59" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R59" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S59" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T59" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="G60" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="H60" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="I60" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J60" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K60" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="L60" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="M60" s="23" t="s">
+        <v>296</v>
+      </c>
+      <c r="N60" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O60" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="P60" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q60" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R60" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S60" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T60" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="G61" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="H61" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="I61" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J61" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="K61" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="L61" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="M61" s="23" t="s">
+        <v>296</v>
+      </c>
+      <c r="N61" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O61" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="P61" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q61" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R61" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S61" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T61" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="G62" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="H62" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I62" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J62" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="K62" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="L62" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="M62" s="23" t="s">
+        <v>296</v>
+      </c>
+      <c r="N62" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O62" s="20" t="s">
+        <v>304</v>
+      </c>
+      <c r="P62" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="Q62" s="19" t="s">
+        <v>305</v>
+      </c>
+      <c r="R62" s="17" t="s">
+        <v>306</v>
+      </c>
+      <c r="S62" s="17" t="s">
+        <v>282</v>
+      </c>
+      <c r="T62" s="16" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="G63" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="H63" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I63" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J63" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K63" s="19" t="s">
+        <v>308</v>
+      </c>
+      <c r="L63" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="M63" s="23" t="s">
+        <v>296</v>
+      </c>
+      <c r="N63" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O63" s="20" t="s">
+        <v>309</v>
+      </c>
+      <c r="P63" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q63" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="R63" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="S63" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="T63" s="16" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B64" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C64" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="D64" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="E64" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F64" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="G64" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="H64" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="I64" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="J64" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K64" s="19" t="s">
+        <v>316</v>
+      </c>
+      <c r="L64" s="23" t="s">
+        <v>317</v>
+      </c>
+      <c r="M64" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="N64" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O64" s="20" t="s">
+        <v>319</v>
+      </c>
+      <c r="P64" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q64" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R64" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S64" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T64" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C65" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="D65" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="E65" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F65" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="G65" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="H65" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I65" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="J65" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="K65" s="19" t="s">
+        <v>320</v>
+      </c>
+      <c r="L65" s="23" t="s">
+        <v>317</v>
+      </c>
+      <c r="M65" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="N65" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O65" s="20" t="s">
+        <v>321</v>
+      </c>
+      <c r="P65" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q65" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R65" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S65" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T65" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B66" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C66" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="D66" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="E66" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F66" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="G66" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="H66" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="I66" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J66" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="K66" s="19" t="s">
+        <v>322</v>
+      </c>
+      <c r="L66" s="23" t="s">
+        <v>317</v>
+      </c>
+      <c r="M66" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="N66" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O66" s="20" t="s">
+        <v>323</v>
+      </c>
+      <c r="P66" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q66" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R66" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S66" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T66" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C67" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="D67" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E67" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F67" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G67" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="H67" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="I67" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J67" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="K67" s="19" t="s">
+        <v>325</v>
+      </c>
+      <c r="L67" s="23" t="s">
+        <v>326</v>
+      </c>
+      <c r="M67" s="23" t="s">
+        <v>327</v>
+      </c>
+      <c r="N67" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O67" s="20" t="s">
+        <v>328</v>
+      </c>
+      <c r="P67" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q67" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R67" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S67" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T67" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B68" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C68" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="D68" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E68" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F68" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G68" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="H68" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="I68" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J68" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K68" s="19" t="s">
+        <v>329</v>
+      </c>
+      <c r="L68" s="23" t="s">
+        <v>326</v>
+      </c>
+      <c r="M68" s="23" t="s">
+        <v>327</v>
+      </c>
+      <c r="N68" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O68" s="20" t="s">
+        <v>330</v>
+      </c>
+      <c r="P68" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q68" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R68" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S68" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T68" s="16" t="s">
         <v>27</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$T$37"/>
+  <autoFilter ref="$A$1:$T$68"/>
   <pageSetup orientation="landscape" paperSize="9"/>
   <headerFooter>
     <oddHeader>&amp;R&amp;P</oddHeader>
